--- a/Redemittel.xlsx
+++ b/Redemittel.xlsx
@@ -4,23 +4,27 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="20400" windowHeight="7980" activeTab="5"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="20400" windowHeight="7515" tabRatio="820" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="zusammen etwas planen" sheetId="3" r:id="rId1"/>
-    <sheet name="Undirekte Frage" sheetId="4" r:id="rId2"/>
-    <sheet name="Hoffliche Satze" sheetId="5" r:id="rId3"/>
-    <sheet name="zusammen etwas planen (voll)" sheetId="1" r:id="rId4"/>
-    <sheet name="Empfehlung" sheetId="8" r:id="rId5"/>
-    <sheet name="Умляуты" sheetId="2" r:id="rId6"/>
-    <sheet name="Лист4" sheetId="7" r:id="rId7"/>
+    <sheet name="Undirekte Frage" sheetId="4" r:id="rId1"/>
+    <sheet name="Hoffliche Satze" sheetId="5" r:id="rId2"/>
+    <sheet name="Meinung und Argument" sheetId="13" r:id="rId3"/>
+    <sheet name="Empfehlung" sheetId="8" r:id="rId4"/>
+    <sheet name="zusammen etwas planen" sheetId="3" r:id="rId5"/>
+    <sheet name="zusammen etwas planen (voll)" sheetId="1" r:id="rId6"/>
+    <sheet name="zusammen etwas planen (voll)2" sheetId="7" r:id="rId7"/>
+    <sheet name="Ideen" sheetId="10" r:id="rId8"/>
+    <sheet name="Умляуты" sheetId="2" r:id="rId9"/>
+    <sheet name="Лист1" sheetId="9" r:id="rId10"/>
+    <sheet name="kurze Fragen und Antworten" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="301">
   <si>
     <t>ö</t>
   </si>
@@ -370,9 +374,6 @@
     <t>Wollen wir … ?</t>
   </si>
   <si>
-    <t>Annahme</t>
-  </si>
-  <si>
     <t>Ablehnung</t>
   </si>
   <si>
@@ -446,9 +447,6 @@
   </si>
   <si>
     <t>Das gefällt mir gut. Ich glaube, [dass]…</t>
-  </si>
-  <si>
-    <t>Einverstanden. So machen wir es./Das machen wie so.</t>
   </si>
   <si>
     <t>Das kommt für mich nich in Frage.</t>
@@ -641,13 +639,546 @@
   </si>
   <si>
     <t>Und wenn das nicht hilft?                                                                                                       In dem Fall wäre es am besten, du bleibst ein paar Tage im Bet.</t>
+  </si>
+  <si>
+    <t>Einverstanden. So machen wir es./Das machen wir so.</t>
+  </si>
+  <si>
+    <t>Annahme (zustimmen)</t>
+  </si>
+  <si>
+    <t>Meinung sagen</t>
+  </si>
+  <si>
+    <t>Meiner Erfahrung nach ist es am besten, wenn …</t>
+  </si>
+  <si>
+    <t>Ich bin der Meinung, dass …</t>
+  </si>
+  <si>
+    <t>Entschuldigung, das habe ich nicht verschstanden. Noch einmal, bitte.</t>
+  </si>
+  <si>
+    <t>Извините, что означает … ?</t>
+  </si>
+  <si>
+    <t>Entschuldigung, was bedeutet … ?</t>
+  </si>
+  <si>
+    <t>Ja, das ist eine gute Idee. Ich möchte auch gerne…</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gutschein</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> für die Buchhandlung - wegen des Interesses an Bücher / das Handelsnetz/die Ladenkette - um etwas geeignete/passende kaufen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Konzertkarte</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - wegen des Interesses an Kultur und Musik. Und wegen der kommenden super Veranstaltungen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>das Souvenir/ das Andenken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - um sich an uns/Ort zu erinnern</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In die Berge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - einfachen Steig machen, die Natur Genissen, Im Internet nach Angeboten rescheschieren, 3 Tage, Jugendherberge/Hotel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moskau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  - Sehenswürdigkeite, Museum, Rundfahrt. Hotel buchen. Mit dem Flugzeug. 5 Tage</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>An den See</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - am Strand, schwiemen, nach einem schönen Platz rescheschieren</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In den Park</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - wegen des schönen Wetter, einige Aktivitäten unternehmen (radfahren, Attraktionen), sich unterchalten, im Café Zeit verbringen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Spaziergang durch die Stadt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - wegen des schönen Wetter, Sehenswürdigkeiten anzuschauen, kurz die Stadt kennenlernen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>An den See</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - wegen des schönen Wetter (laut Wetterbericht), nich weit von hier, am Strand, schwiemen, nach einem schönen Platz rescheschieren, ein paar Sandwiches un Säfte mitbringen.</t>
+    </r>
+  </si>
+  <si>
+    <t>der Blumenstrauß</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Chat mit anderen das mittelen, wenn alle einverstanden - Kosten erfahren, wenn geteilte Kosten allen passen - kaufen </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Museum mit Bilder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - wegen des Interesses an der Kunst, nach interessanten Ausstellungen rescheschieren, Kosten von Eintrittkarten erfahren, Eintrittkarten kaufen, </t>
+    </r>
+  </si>
+  <si>
+    <t>Geschenke</t>
+  </si>
+  <si>
+    <t>Ausflug</t>
+  </si>
+  <si>
+    <t>Reise</t>
+  </si>
+  <si>
+    <t>Jemandem mit Renovierung helfen</t>
+  </si>
+  <si>
+    <t>Jemandem mit Umziehung helfen</t>
+  </si>
+  <si>
+    <t>nach Mittel im Fachmarkt rescheschieren (Bürste)</t>
+  </si>
+  <si>
+    <t>alte Kleidung mitbringen</t>
+  </si>
+  <si>
+    <t>mit der Wahl der Farben helfen</t>
+  </si>
+  <si>
+    <t>selbst Putzen oder Putzleistung</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Wände streichen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>ein paar Sandwiches un Säfte mitbringen.</t>
+  </si>
+  <si>
+    <t>Kartons un Tüten mitbringen</t>
+  </si>
+  <si>
+    <t>nach einen gunstigen Wagen suchen/rescheschieren (im Internet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mit anderen  im Chat mittelen - wer mithelfen möchte - immer willkommen </t>
+  </si>
+  <si>
+    <t>Sachen einpacken und dann auspacken</t>
+  </si>
+  <si>
+    <t>Jemandem mit Kind helfen</t>
+  </si>
+  <si>
+    <t>Meiner Auffassung/Meinung/Ansicht nach</t>
+  </si>
+  <si>
+    <t>Meines Erachtens …</t>
+  </si>
+  <si>
+    <t>Ich bin der festen Überzeugung, dass …</t>
+  </si>
+  <si>
+    <t>Ich finde/denke/glaube/meine, dass …</t>
+  </si>
+  <si>
+    <t>Meine Meinung dazu ist, dass …</t>
+  </si>
+  <si>
+    <t>Für mich ist richtig/falsch, dass …</t>
+  </si>
+  <si>
+    <t>Auf der einen Seite …., auf der anderen Seite / einerseits … andererseits</t>
+  </si>
+  <si>
+    <t>In Bezug auf … würde ich sagen …</t>
+  </si>
+  <si>
+    <t>Ich vertrete folgenden Standpunkt:</t>
+  </si>
+  <si>
+    <t>Ich persönliche denke …</t>
+  </si>
+  <si>
+    <t>Für mich überwiegen die Vorteile/Nachteile</t>
+  </si>
+  <si>
+    <t>Es ist von Vorteil, dass …</t>
+  </si>
+  <si>
+    <t>Ich finde es vorteilhaft, dass … / ich finde es nachteilich, dass …</t>
+  </si>
+  <si>
+    <t>Ein wichtiger/bedeutsamer/wesentlicher Aspekt, der dafür/dagegen spricht, ist …</t>
+  </si>
+  <si>
+    <t>der Hauptvorteil ist …, der Hauptnachteil ist …</t>
+  </si>
+  <si>
+    <t>Dafür/dagegen spricht auch, dass …</t>
+  </si>
+  <si>
+    <t>Ich halte es für vorteilhaft, dass …</t>
+  </si>
+  <si>
+    <t>Das entscheidende Argument, das für/gegen ... spricht, ist für mich …</t>
+  </si>
+  <si>
+    <t>Das stimmt aber nicht!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hast du den Regen erwischt? </t>
+  </si>
+  <si>
+    <t>Knapp vorbeigeschrammt. Du wohl nicht.</t>
+  </si>
+  <si>
+    <t>Ja. Nur nicht planen, einfach machen.</t>
+  </si>
+  <si>
+    <t>Findest du, wir sollten öfter so quatschen?</t>
+  </si>
+  <si>
+    <t>Bist du heute Morgen auch schlecht hochgekommen?</t>
+  </si>
+  <si>
+    <t>Ohne Kaffe wäre ich noch im Bett.</t>
+  </si>
+  <si>
+    <t>Warum seufzt du gerade?</t>
+  </si>
+  <si>
+    <t>Schon wieder ein Tab zu viel im Kopf.</t>
+  </si>
+  <si>
+    <t>Nervt dich das auch?</t>
+  </si>
+  <si>
+    <t>Total. Und ich darf nicht mal laut sagen, was ich denke</t>
+  </si>
+  <si>
+    <t>Magst du Überraschungen?</t>
+  </si>
+  <si>
+    <t>Kommt darauf an. Nicht um 8 Uhr morgens.</t>
+  </si>
+  <si>
+    <t>Schon wieder Montag, oder?</t>
+  </si>
+  <si>
+    <t>Leider. Das Wochenende war ein guter Freund.</t>
+  </si>
+  <si>
+    <t>Findest du, man sollte öfter einfach nichts tun?</t>
+  </si>
+  <si>
+    <t>Absolut. Nichtstun ist auch eine Leistung.</t>
+  </si>
+  <si>
+    <t>Was machst du gleich nach Feierabend?</t>
+  </si>
+  <si>
+    <t>Tief durchatmen. Dann mal sehen.</t>
+  </si>
+  <si>
+    <t>Hast du noch Energy für heute Abend?</t>
+  </si>
+  <si>
+    <t>Exakt für eine Folge. Dann ist Schluss.</t>
+  </si>
+  <si>
+    <t>Kann ich dich kurz was fragen?</t>
+  </si>
+  <si>
+    <t>Hast du gerade. Weiter.</t>
+  </si>
+  <si>
+    <t>Kann man hier irgendwo die Seele baumeln lasen.</t>
+  </si>
+  <si>
+    <t>Hinter links. Gute Ecke.</t>
+  </si>
+  <si>
+    <t>Ist dein Tag auch so voll?</t>
+  </si>
+  <si>
+    <t>Voller als mein Kühlschrank, und der ist leer.</t>
+  </si>
+  <si>
+    <t>Bleibst noch länger?</t>
+  </si>
+  <si>
+    <t>Eher nicht. Meine Couch ruft.</t>
+  </si>
+  <si>
+    <t>Schon was vor am Wochenende?</t>
+  </si>
+  <si>
+    <t>Bis jetzt nichts Festes. Und selbst?</t>
+  </si>
+  <si>
+    <t>In dem Punkt würde ich dir nur zustimmen.</t>
+  </si>
+  <si>
+    <t>Da hats du natürlich Recht.</t>
+  </si>
+  <si>
+    <t>Das ist wirklich ein schlagendes Argument</t>
+  </si>
+  <si>
+    <t>Dein Argument leuchtet mir ein.</t>
+  </si>
+  <si>
+    <t>Ich teile deine Meinung vollkommen.</t>
+  </si>
+  <si>
+    <t>Wie du eben selbst richtig gesagt hast, …</t>
+  </si>
+  <si>
+    <t>Da hast du vollkommen Recht. Dem kann ich nur zustimmen.</t>
+  </si>
+  <si>
+    <t>Dieses Argument finde ich unbestritten.</t>
+  </si>
+  <si>
+    <t>Was für eins Brauchst du denn?</t>
+  </si>
+  <si>
+    <t>Das darf nich wahr sein!</t>
+  </si>
+  <si>
+    <t>Das gibt's doch nicht!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,8 +1227,17 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,6 +1256,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -729,7 +1275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -755,12 +1301,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -768,6 +1314,96 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6146" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6858000" y="0"/>
+          <a:ext cx="14849475" cy="5819775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2050" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14658975" cy="5762625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1055,7 +1691,551 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75">
+      <c r="A1" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18.75">
+      <c r="A2" s="15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="18.75">
+      <c r="A3" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="18.75">
+      <c r="A4" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="112.85546875" style="17" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.75">
+      <c r="A1" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18.75">
+      <c r="E2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="31.5">
+      <c r="A3" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75">
+      <c r="E4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30.75">
+      <c r="A7" s="17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30.75">
+      <c r="A9" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="17" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="17" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="17" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="17" t="s">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="65.140625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="68.5703125" style="15" customWidth="1"/>
+    <col min="3" max="6" width="9.140625" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75">
+      <c r="A1" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18.75">
+      <c r="A2" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A30"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="102.5703125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="74.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="20" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="20" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="15" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="15" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="15" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="15" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="77.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75">
+      <c r="A1" s="15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A2" s="15"/>
+    </row>
+    <row r="3" spans="1:1" ht="37.5">
+      <c r="A3" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="18.75">
+      <c r="A4" s="15"/>
+    </row>
+    <row r="5" spans="1:1" ht="18.75">
+      <c r="A5" s="15"/>
+    </row>
+    <row r="6" spans="1:1" ht="18.75">
+      <c r="A6" s="15"/>
+    </row>
+    <row r="7" spans="1:1" ht="18.75">
+      <c r="A7" s="15"/>
+    </row>
+    <row r="8" spans="1:1" ht="18.75">
+      <c r="A8" s="15"/>
+    </row>
+    <row r="9" spans="1:1" ht="18.75">
+      <c r="A9" s="15"/>
+    </row>
+    <row r="10" spans="1:1" ht="18.75">
+      <c r="A10" s="15"/>
+    </row>
+    <row r="11" spans="1:1" ht="18.75">
+      <c r="A11" s="15"/>
+    </row>
+    <row r="12" spans="1:1" ht="18.75">
+      <c r="A12" s="15"/>
+    </row>
+    <row r="13" spans="1:1" ht="18.75">
+      <c r="A13" s="15"/>
+    </row>
+    <row r="14" spans="1:1" ht="18.75">
+      <c r="A14" s="15"/>
+    </row>
+    <row r="15" spans="1:1" ht="18.75">
+      <c r="A15" s="15"/>
+    </row>
+    <row r="16" spans="1:1" ht="18.75">
+      <c r="A16" s="15"/>
+    </row>
+    <row r="17" spans="1:1" ht="18.75">
+      <c r="A17" s="15"/>
+    </row>
+    <row r="18" spans="1:1" ht="18.75">
+      <c r="A18" s="15"/>
+    </row>
+    <row r="19" spans="1:1" ht="18.75">
+      <c r="A19" s="15"/>
+    </row>
+    <row r="20" spans="1:1" ht="18.75">
+      <c r="A20" s="15"/>
+    </row>
+    <row r="21" spans="1:1" ht="18.75">
+      <c r="A21" s="15"/>
+    </row>
+    <row r="22" spans="1:1" ht="18.75">
+      <c r="A22" s="15"/>
+    </row>
+    <row r="23" spans="1:1" ht="18.75">
+      <c r="A23" s="15"/>
+    </row>
+    <row r="24" spans="1:1" ht="18.75">
+      <c r="A24" s="15"/>
+    </row>
+    <row r="25" spans="1:1" ht="18.75">
+      <c r="A25" s="15"/>
+    </row>
+    <row r="26" spans="1:1" ht="18.75">
+      <c r="A26" s="15"/>
+    </row>
+    <row r="27" spans="1:1" ht="18.75">
+      <c r="A27" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="76" style="7" customWidth="1"/>
@@ -1079,15 +2259,15 @@
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1">
@@ -1117,23 +2297,23 @@
         <v>10</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
@@ -1146,7 +2326,7 @@
     </row>
     <row r="12" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>13</v>
@@ -1176,155 +2356,185 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="2" customFormat="1">
+    <row r="16" spans="1:2" s="14" customFormat="1" ht="21.75" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="11"/>
-    </row>
-    <row r="17" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A17" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="15"/>
+    </row>
+    <row r="17" spans="1:2" s="14" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" s="15"/>
+    </row>
+    <row r="18" spans="1:2" s="14" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="15"/>
+    </row>
+    <row r="19" spans="1:2" s="14" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+    </row>
+    <row r="20" spans="1:2" s="2" customFormat="1">
+      <c r="A20" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A19" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" s="2" customFormat="1">
-      <c r="A21" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="11"/>
+      <c r="B21" s="15" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="22" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" s="2" customFormat="1" ht="18.75">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" s="2" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" s="2" customFormat="1">
-      <c r="A26" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="11"/>
+        <v>131</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" s="2" customFormat="1">
+      <c r="A25" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="11"/>
+    </row>
+    <row r="26" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="27" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" s="2" customFormat="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" s="2" customFormat="1" ht="18.75">
-      <c r="A30" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>121</v>
-      </c>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="2" customFormat="1" ht="48.75" customHeight="1">
+      <c r="A29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" s="2" customFormat="1">
+      <c r="A30" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="11"/>
     </row>
     <row r="31" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" s="2" customFormat="1">
-      <c r="A32" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B32" s="11"/>
+        <v>88</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" s="14" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="33" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" s="2" customFormat="1" ht="18.75">
+      <c r="A35" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" s="2" customFormat="1">
+      <c r="A37" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="11"/>
+    </row>
+    <row r="38" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A39" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A35" s="4" t="s">
+    <row r="40" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A40" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1334,63 +2544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="63.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
-      <c r="A1" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="18.75">
-      <c r="A2" s="15" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="18.75">
-      <c r="A3" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="18.75">
-      <c r="A4" s="15" t="s">
-        <v>197</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
-      <c r="A1" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="18.75">
-      <c r="A2" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1430,10 +2584,10 @@
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="21.75" customHeight="1">
@@ -1478,26 +2632,26 @@
     </row>
     <row r="11" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="21.75" customHeight="1">
@@ -1510,18 +2664,18 @@
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="21.75" customHeight="1">
@@ -1550,18 +2704,18 @@
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
@@ -1570,26 +2724,26 @@
     </row>
     <row r="23" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="21.75" customHeight="1">
@@ -1602,18 +2756,18 @@
     </row>
     <row r="27" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="21.75" customHeight="1">
@@ -1621,7 +2775,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="21.75" customHeight="1">
@@ -1666,10 +2820,10 @@
     </row>
     <row r="35" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="21.75" customHeight="1">
@@ -1746,16 +2900,16 @@
     </row>
     <row r="45" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="21.75" customHeight="1">
@@ -1768,34 +2922,34 @@
     </row>
     <row r="48" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="21.75" customHeight="1">
@@ -1816,34 +2970,34 @@
     </row>
     <row r="54" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="21.75" customHeight="1">
@@ -1904,10 +3058,10 @@
     </row>
     <row r="65" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="21.75" customHeight="1">
@@ -1976,10 +3130,10 @@
     </row>
     <row r="74" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A74" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="21.75" customHeight="1">
@@ -2032,10 +3186,10 @@
     </row>
     <row r="81" spans="1:2" s="2" customFormat="1" ht="21.75" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="21.75" customHeight="1">
@@ -2179,71 +3333,6 @@
     <row r="117" spans="1:2" ht="21.75" customHeight="1"/>
     <row r="118" spans="1:2" ht="21.75" customHeight="1"/>
     <row r="119" spans="1:2" ht="21.75" customHeight="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="68.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="14" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="14" customFormat="1"/>
-    <row r="3" spans="1:1" ht="30">
-      <c r="A3" s="17" t="s">
-        <v>205</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18.75">
-      <c r="A2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18.75">
-      <c r="A3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18.75">
-      <c r="A4" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2259,40 +3348,426 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75">
-      <c r="A1" s="13" t="s">
-        <v>199</v>
-      </c>
+      <c r="A1" s="13"/>
     </row>
     <row r="2" spans="1:1" s="14" customFormat="1" ht="15.75">
       <c r="A2" s="13"/>
     </row>
-    <row r="3" spans="1:1" ht="30.75">
-      <c r="A3" s="18" t="s">
-        <v>200</v>
-      </c>
+    <row r="3" spans="1:1" ht="15.75">
+      <c r="A3" s="17"/>
     </row>
     <row r="4" spans="1:1" s="14" customFormat="1" ht="15.75">
-      <c r="A4" s="18"/>
+      <c r="A4" s="17"/>
     </row>
     <row r="5" spans="1:1" ht="15.75">
-      <c r="A5" s="13" t="s">
-        <v>201</v>
-      </c>
+      <c r="A5" s="13"/>
     </row>
     <row r="6" spans="1:1" s="14" customFormat="1" ht="15.75">
       <c r="A6" s="13"/>
     </row>
-    <row r="7" spans="1:1" ht="30.75">
-      <c r="A7" s="18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="30.75">
-      <c r="A9" s="18" t="s">
-        <v>203</v>
-      </c>
+    <row r="7" spans="1:1" ht="15.75">
+      <c r="A7" s="17"/>
+    </row>
+    <row r="9" spans="1:1" ht="15.75">
+      <c r="A9" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F93"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="217.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="19" customFormat="1" ht="18.75">
+      <c r="A1" s="19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="14" customFormat="1"/>
+    <row r="3" spans="1:1" ht="18.75">
+      <c r="A3" s="15" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="18.75">
+      <c r="A4" s="15"/>
+    </row>
+    <row r="5" spans="1:1" ht="18.75">
+      <c r="A5" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="18.75">
+      <c r="A6" s="15"/>
+    </row>
+    <row r="7" spans="1:1" ht="18.75">
+      <c r="A7" s="15" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="18.75">
+      <c r="A8" s="15"/>
+    </row>
+    <row r="9" spans="1:1" ht="18.75">
+      <c r="A9" s="18" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="18.75">
+      <c r="A10" s="15"/>
+    </row>
+    <row r="11" spans="1:1" ht="18.75">
+      <c r="A11" s="15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="18.75">
+      <c r="A12" s="15"/>
+    </row>
+    <row r="13" spans="1:1" ht="18.75">
+      <c r="A13" s="15"/>
+    </row>
+    <row r="14" spans="1:1" ht="18.75">
+      <c r="A14" s="19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="18.75">
+      <c r="A15" s="15"/>
+    </row>
+    <row r="16" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A16" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A17" s="15"/>
+    </row>
+    <row r="18" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A18" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A19" s="15"/>
+    </row>
+    <row r="20" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A20" s="15" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A21" s="15"/>
+    </row>
+    <row r="22" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A22" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="D23" s="14"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="D24" s="14"/>
+      <c r="F24" s="14"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75">
+      <c r="A25" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75">
+      <c r="A26" s="15"/>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A27" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A28" s="15"/>
+    </row>
+    <row r="29" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A29" s="15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A30" s="15"/>
+    </row>
+    <row r="31" spans="1:6" s="14" customFormat="1" ht="18.75">
+      <c r="A31" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18.75">
+      <c r="A32" s="15"/>
+    </row>
+    <row r="33" spans="1:1" ht="18.75">
+      <c r="A33" s="15"/>
+    </row>
+    <row r="34" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A34" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A35" s="15"/>
+    </row>
+    <row r="36" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A36" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A37" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A38" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A39" s="15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A40" s="15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A41" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A42" s="15"/>
+    </row>
+    <row r="43" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A43" s="15"/>
+    </row>
+    <row r="44" spans="1:1" s="19" customFormat="1" ht="18.75">
+      <c r="A44" s="19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A45" s="15"/>
+    </row>
+    <row r="46" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A46" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="18.75">
+      <c r="A47" s="15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="18.75">
+      <c r="A48" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="18.75">
+      <c r="A49" s="15" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="18.75">
+      <c r="A50" s="15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="18.75">
+      <c r="A51" s="15"/>
+    </row>
+    <row r="52" spans="1:1" ht="18.75">
+      <c r="A52" s="15"/>
+    </row>
+    <row r="53" spans="1:1" s="19" customFormat="1" ht="18.75">
+      <c r="A53" s="19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A54" s="15"/>
+    </row>
+    <row r="55" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A55" s="15"/>
+    </row>
+    <row r="56" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A56" s="15"/>
+    </row>
+    <row r="57" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A57" s="15"/>
+    </row>
+    <row r="58" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A58" s="15"/>
+    </row>
+    <row r="59" spans="1:1" s="14" customFormat="1" ht="18.75">
+      <c r="A59" s="15"/>
+    </row>
+    <row r="60" spans="1:1" ht="18.75">
+      <c r="A60" s="15"/>
+    </row>
+    <row r="61" spans="1:1" ht="18.75">
+      <c r="A61" s="15"/>
+    </row>
+    <row r="62" spans="1:1" ht="18.75">
+      <c r="A62" s="15"/>
+    </row>
+    <row r="63" spans="1:1" ht="18.75">
+      <c r="A63" s="15"/>
+    </row>
+    <row r="64" spans="1:1" ht="18.75">
+      <c r="A64" s="15"/>
+    </row>
+    <row r="65" spans="1:1" ht="18.75">
+      <c r="A65" s="15"/>
+    </row>
+    <row r="66" spans="1:1" ht="18.75">
+      <c r="A66" s="15"/>
+    </row>
+    <row r="67" spans="1:1" ht="18.75">
+      <c r="A67" s="15"/>
+    </row>
+    <row r="68" spans="1:1" ht="18.75">
+      <c r="A68" s="15"/>
+    </row>
+    <row r="69" spans="1:1" ht="18.75">
+      <c r="A69" s="15"/>
+    </row>
+    <row r="70" spans="1:1" ht="18.75">
+      <c r="A70" s="15"/>
+    </row>
+    <row r="71" spans="1:1" ht="18.75">
+      <c r="A71" s="15"/>
+    </row>
+    <row r="72" spans="1:1" ht="18.75">
+      <c r="A72" s="15"/>
+    </row>
+    <row r="73" spans="1:1" ht="18.75">
+      <c r="A73" s="15"/>
+    </row>
+    <row r="74" spans="1:1" ht="18.75">
+      <c r="A74" s="15"/>
+    </row>
+    <row r="75" spans="1:1" ht="18.75">
+      <c r="A75" s="15"/>
+    </row>
+    <row r="76" spans="1:1" ht="18.75">
+      <c r="A76" s="15"/>
+    </row>
+    <row r="77" spans="1:1" ht="18.75">
+      <c r="A77" s="15"/>
+    </row>
+    <row r="78" spans="1:1" ht="18.75">
+      <c r="A78" s="15"/>
+    </row>
+    <row r="79" spans="1:1" ht="18.75">
+      <c r="A79" s="15"/>
+    </row>
+    <row r="80" spans="1:1" ht="18.75">
+      <c r="A80" s="15"/>
+    </row>
+    <row r="81" spans="1:1" ht="18.75">
+      <c r="A81" s="15"/>
+    </row>
+    <row r="82" spans="1:1" ht="18.75">
+      <c r="A82" s="15"/>
+    </row>
+    <row r="83" spans="1:1" ht="18.75">
+      <c r="A83" s="15"/>
+    </row>
+    <row r="84" spans="1:1" ht="18.75">
+      <c r="A84" s="15"/>
+    </row>
+    <row r="85" spans="1:1" ht="18.75">
+      <c r="A85" s="15"/>
+    </row>
+    <row r="86" spans="1:1" ht="18.75">
+      <c r="A86" s="15"/>
+    </row>
+    <row r="87" spans="1:1" ht="18.75">
+      <c r="A87" s="15"/>
+    </row>
+    <row r="88" spans="1:1" ht="18.75">
+      <c r="A88" s="15"/>
+    </row>
+    <row r="89" spans="1:1" ht="18.75">
+      <c r="A89" s="15"/>
+    </row>
+    <row r="90" spans="1:1" ht="18.75">
+      <c r="A90" s="15"/>
+    </row>
+    <row r="91" spans="1:1" ht="18.75">
+      <c r="A91" s="15"/>
+    </row>
+    <row r="92" spans="1:1" ht="18.75">
+      <c r="A92" s="15"/>
+    </row>
+    <row r="93" spans="1:1" ht="18.75">
+      <c r="A93" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18.75">
+      <c r="A2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18.75">
+      <c r="A3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18.75">
+      <c r="A4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Redemittel.xlsx
+++ b/Redemittel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="20400" windowHeight="7515" tabRatio="820" activeTab="2"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="20400" windowHeight="7515" tabRatio="807" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Undirekte Frage" sheetId="4" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="302">
   <si>
     <t>ö</t>
   </si>
@@ -1172,6 +1172,9 @@
   </si>
   <si>
     <t>Das gibt's doch nicht!</t>
+  </si>
+  <si>
+    <t>Aus dem Alltag ausbrechen</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="112.85546875" style="17" customWidth="1"/>
@@ -1800,6 +1803,11 @@
     <row r="17" spans="1:1">
       <c r="A17" s="17" t="s">
         <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="17" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/Redemittel.xlsx
+++ b/Redemittel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="20400" windowHeight="7515" tabRatio="807" activeTab="9"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="20400" windowHeight="7515" tabRatio="807" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Undirekte Frage" sheetId="4" r:id="rId1"/>
